--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
@@ -1201,7 +1201,7 @@
         <v>1.111747436896048</v>
       </c>
       <c r="H32">
-        <v>1.046292170658181</v>
+        <v>1.04629217065818</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2475,7 +2475,7 @@
         <v>1.015295864229556</v>
       </c>
       <c r="H81">
-        <v>0.9874870185077534</v>
+        <v>0.9874870185077536</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2593,7 +2593,7 @@
         <v>1.196516514821118</v>
       </c>
       <c r="D86">
-        <v>0.2213949811121383</v>
+        <v>0.2213949811121382</v>
       </c>
       <c r="E86">
         <v>0.9313147727988539</v>
@@ -4098,7 +4098,7 @@
         <v>1.681820707759932</v>
       </c>
       <c r="C144">
-        <v>1.571654911485923</v>
+        <v>1.571654911485924</v>
       </c>
       <c r="D144">
         <v>1.630925900008794</v>
@@ -7233,7 +7233,7 @@
         <v>0.6038150790861716</v>
       </c>
       <c r="H264">
-        <v>0.547732947946552</v>
+        <v>0.5477329479465519</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7311,7 +7311,7 @@
         <v>0.3745437349761055</v>
       </c>
       <c r="H267">
-        <v>0.3397562452462323</v>
+        <v>0.3397562452462322</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7389,7 +7389,7 @@
         <v>0.689346481502188</v>
       </c>
       <c r="H270">
-        <v>0.6336281921428406</v>
+        <v>0.6336281921428405</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7455,7 +7455,7 @@
         <v>0.7935785139177227</v>
       </c>
       <c r="D273">
-        <v>0.2691253133179039</v>
+        <v>0.2691253133179038</v>
       </c>
       <c r="E273">
         <v>0.5821306037918371</v>
@@ -7507,7 +7507,7 @@
         <v>0.6081291775491042</v>
       </c>
       <c r="D275">
-        <v>0.7105771605952497</v>
+        <v>0.7105771605952498</v>
       </c>
       <c r="E275">
         <v>0.6342580037945716</v>
@@ -8033,7 +8033,7 @@
         <v>0.7631640066069848</v>
       </c>
       <c r="F295">
-        <v>0.8174381810071055</v>
+        <v>0.8174381810071056</v>
       </c>
       <c r="G295">
         <v>0.6887390219712166</v>
@@ -8137,7 +8137,7 @@
         <v>1.01366597725708</v>
       </c>
       <c r="F299">
-        <v>0.8941391955291627</v>
+        <v>0.8941391955291628</v>
       </c>
       <c r="G299">
         <v>0.9834503948191701</v>
@@ -8163,7 +8163,7 @@
         <v>0.6955240972437298</v>
       </c>
       <c r="F300">
-        <v>0.7449879029610935</v>
+        <v>0.7449879029610936</v>
       </c>
       <c r="G300">
         <v>0.6276954656481247</v>
@@ -11300,7 +11300,7 @@
         <v>0.749700826759413</v>
       </c>
       <c r="C421">
-        <v>0.7169244950076398</v>
+        <v>0.7169244950076397</v>
       </c>
       <c r="D421">
         <v>0.8459903494317423</v>
@@ -11404,7 +11404,7 @@
         <v>0.7575636261280708</v>
       </c>
       <c r="C425">
-        <v>0.7244435389589284</v>
+        <v>0.7244435389589283</v>
       </c>
       <c r="D425">
         <v>0.8548630252351763</v>
@@ -12664,7 +12664,7 @@
         <v>0.4736494064979972</v>
       </c>
       <c r="G473">
-        <v>0.4568402508427458</v>
+        <v>0.4568402508427459</v>
       </c>
       <c r="H473">
         <v>0.4606412187966662</v>
